--- a/icon.xlsx
+++ b/icon.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\VSCode\Test\my-vue-app\public\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{628EC6CC-D95E-4CFE-975C-2CEA86C69718}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D0958D54-C3E7-476F-89C5-267FDB8E4271}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-14400" yWindow="0" windowWidth="14400" windowHeight="15600" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="908" uniqueCount="903">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="908" uniqueCount="904">
   <si>
     <t>Name</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -3454,6 +3454,10 @@
   </si>
   <si>
     <t>https://img.gamewith.jp/img/bcc9413f2329bc5ab81fb666b42b67b5.jpg</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://img.gamewith.jp/img/9630e5ccadd4424ccfe7cc32528ea067.jpg</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -6052,7 +6056,7 @@
         <v>560</v>
       </c>
       <c r="B281" s="1" t="s">
-        <v>559</v>
+        <v>903</v>
       </c>
     </row>
     <row r="282" spans="1:2" x14ac:dyDescent="0.25">

--- a/icon.xlsx
+++ b/icon.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\VSCode\Test\my-vue-app\public\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D0958D54-C3E7-476F-89C5-267FDB8E4271}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7AA2836F-C755-4E2B-8C91-AC16B6E86F49}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="908" uniqueCount="904">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="910" uniqueCount="907">
   <si>
     <t>Name</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -3458,6 +3458,18 @@
   </si>
   <si>
     <t>https://img.gamewith.jp/img/9630e5ccadd4424ccfe7cc32528ea067.jpg</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>栗子</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://img.gamewith.jp/img/30b9a40ef0d48bf05e014aea7af66593.jpg</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://img.gamewith.jp/img/a0ec8ef502b57040f9c6390c4fdd1368.jpg</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -3804,7 +3816,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B454"/>
+  <dimension ref="A1:B455"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="18" bestFit="1" customWidth="1"/>
@@ -4600,7 +4612,7 @@
         <v>182</v>
       </c>
       <c r="B99" s="1" t="s">
-        <v>365</v>
+        <v>906</v>
       </c>
     </row>
     <row r="100" spans="1:2" x14ac:dyDescent="0.25">
@@ -7441,6 +7453,14 @@
       </c>
       <c r="B454" s="1" t="s">
         <v>886</v>
+      </c>
+    </row>
+    <row r="455" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A455" s="2" t="s">
+        <v>904</v>
+      </c>
+      <c r="B455" s="1" t="s">
+        <v>905</v>
       </c>
     </row>
   </sheetData>
@@ -7896,8 +7916,9 @@
     <hyperlink ref="B445" r:id="rId448" xr:uid="{EC4BBD61-C148-4666-9C2E-FBE25F581483}"/>
     <hyperlink ref="B446" r:id="rId449" xr:uid="{63EEC303-0702-49D1-990A-4F3D6D45FCD2}"/>
     <hyperlink ref="B431" r:id="rId450" xr:uid="{7434BEB5-05D4-4B2C-8F9D-02E50A6A1774}"/>
+    <hyperlink ref="B455" r:id="rId451" xr:uid="{DF44BD09-B90C-4D51-BB08-67197608024B}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId451"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId452"/>
 </worksheet>
 </file>